--- a/ui_runner/templates/graded_analysis_tabs_2026-05-20.xlsx
+++ b/ui_runner/templates/graded_analysis_tabs_2026-05-20.xlsx
@@ -500,16 +500,16 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>56</v>
+        <v>64</v>
       </c>
       <c r="E3" t="n">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="F3" t="n">
-        <v>27</v>
+        <v>31</v>
       </c>
       <c r="G3" t="n">
-        <v>51.8</v>
+        <v>51.6</v>
       </c>
     </row>
     <row r="4">
@@ -529,16 +529,16 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="E4" t="n">
         <v>12</v>
       </c>
       <c r="F4" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="G4" t="n">
-        <v>52.2</v>
+        <v>50</v>
       </c>
     </row>
     <row r="5">
@@ -558,16 +558,16 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="E5" t="n">
         <v>33</v>
       </c>
       <c r="F5" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="G5" t="n">
-        <v>64.7</v>
+        <v>63.5</v>
       </c>
     </row>
     <row r="6">
@@ -587,16 +587,16 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="E6" t="n">
         <v>19</v>
       </c>
       <c r="F6" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="G6" t="n">
-        <v>61.3</v>
+        <v>59.4</v>
       </c>
     </row>
     <row r="7">
@@ -645,16 +645,16 @@
         </is>
       </c>
       <c r="D8" t="n">
-        <v>828</v>
+        <v>831</v>
       </c>
       <c r="E8" t="n">
-        <v>266</v>
+        <v>268</v>
       </c>
       <c r="F8" t="n">
-        <v>562</v>
+        <v>563</v>
       </c>
       <c r="G8" t="n">
-        <v>32.1</v>
+        <v>32.3</v>
       </c>
     </row>
     <row r="9">
@@ -674,16 +674,16 @@
         </is>
       </c>
       <c r="D9" t="n">
-        <v>177</v>
+        <v>179</v>
       </c>
       <c r="E9" t="n">
         <v>81</v>
       </c>
       <c r="F9" t="n">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="G9" t="n">
-        <v>45.8</v>
+        <v>45.3</v>
       </c>
     </row>
     <row r="10">
@@ -703,16 +703,16 @@
         </is>
       </c>
       <c r="D10" t="n">
-        <v>550</v>
+        <v>574</v>
       </c>
       <c r="E10" t="n">
-        <v>337</v>
+        <v>351</v>
       </c>
       <c r="F10" t="n">
-        <v>213</v>
+        <v>223</v>
       </c>
       <c r="G10" t="n">
-        <v>61.3</v>
+        <v>61.1</v>
       </c>
     </row>
     <row r="11">
@@ -732,16 +732,16 @@
         </is>
       </c>
       <c r="D11" t="n">
-        <v>313</v>
+        <v>324</v>
       </c>
       <c r="E11" t="n">
-        <v>210</v>
+        <v>213</v>
       </c>
       <c r="F11" t="n">
-        <v>103</v>
+        <v>111</v>
       </c>
       <c r="G11" t="n">
-        <v>67.09999999999999</v>
+        <v>65.7</v>
       </c>
     </row>
     <row r="12">
@@ -761,16 +761,16 @@
         </is>
       </c>
       <c r="D12" t="n">
-        <v>137</v>
+        <v>146</v>
       </c>
       <c r="E12" t="n">
-        <v>84</v>
+        <v>90</v>
       </c>
       <c r="F12" t="n">
-        <v>53</v>
+        <v>56</v>
       </c>
       <c r="G12" t="n">
-        <v>61.3</v>
+        <v>61.6</v>
       </c>
     </row>
     <row r="13">
@@ -790,16 +790,16 @@
         </is>
       </c>
       <c r="D13" t="n">
-        <v>295</v>
+        <v>302</v>
       </c>
       <c r="E13" t="n">
-        <v>174</v>
+        <v>180</v>
       </c>
       <c r="F13" t="n">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="G13" t="n">
-        <v>59</v>
+        <v>59.6</v>
       </c>
     </row>
     <row r="14">
@@ -819,16 +819,16 @@
         </is>
       </c>
       <c r="D14" t="n">
-        <v>179</v>
+        <v>190</v>
       </c>
       <c r="E14" t="n">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="F14" t="n">
-        <v>139</v>
+        <v>146</v>
       </c>
       <c r="G14" t="n">
-        <v>22.3</v>
+        <v>23.2</v>
       </c>
     </row>
     <row r="15">
@@ -848,16 +848,16 @@
         </is>
       </c>
       <c r="D15" t="n">
-        <v>162</v>
+        <v>177</v>
       </c>
       <c r="E15" t="n">
-        <v>28</v>
+        <v>33</v>
       </c>
       <c r="F15" t="n">
-        <v>134</v>
+        <v>144</v>
       </c>
       <c r="G15" t="n">
-        <v>17.3</v>
+        <v>18.6</v>
       </c>
     </row>
     <row r="16">
@@ -877,16 +877,16 @@
         </is>
       </c>
       <c r="D16" t="n">
-        <v>93</v>
+        <v>96</v>
       </c>
       <c r="E16" t="n">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="F16" t="n">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="G16" t="n">
-        <v>28</v>
+        <v>29.2</v>
       </c>
     </row>
     <row r="17">
@@ -906,13 +906,13 @@
         </is>
       </c>
       <c r="D17" t="n">
-        <v>2892</v>
+        <v>3007</v>
       </c>
       <c r="E17" t="n">
-        <v>552</v>
+        <v>575</v>
       </c>
       <c r="F17" t="n">
-        <v>2340</v>
+        <v>2432</v>
       </c>
       <c r="G17" t="n">
         <v>19.1</v>
@@ -1525,52 +1525,52 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>61.3</v>
+        <v>61.1</v>
       </c>
       <c r="C7" t="n">
-        <v>550</v>
+        <v>574</v>
       </c>
       <c r="D7" t="n">
-        <v>67.09999999999999</v>
+        <v>65.7</v>
       </c>
       <c r="E7" t="n">
-        <v>313</v>
+        <v>324</v>
       </c>
       <c r="F7" t="n">
-        <v>61.3</v>
+        <v>61.6</v>
       </c>
       <c r="G7" t="n">
-        <v>137</v>
+        <v>146</v>
       </c>
       <c r="H7" t="n">
-        <v>59</v>
+        <v>59.6</v>
       </c>
       <c r="I7" t="n">
-        <v>295</v>
+        <v>302</v>
       </c>
       <c r="J7" t="n">
-        <v>22.3</v>
+        <v>23.2</v>
       </c>
       <c r="K7" t="n">
-        <v>179</v>
+        <v>190</v>
       </c>
       <c r="L7" t="n">
-        <v>17.3</v>
+        <v>18.6</v>
       </c>
       <c r="M7" t="n">
-        <v>162</v>
+        <v>177</v>
       </c>
       <c r="N7" t="n">
-        <v>28</v>
+        <v>29.2</v>
       </c>
       <c r="O7" t="n">
-        <v>93</v>
+        <v>96</v>
       </c>
       <c r="P7" t="n">
         <v>19.1</v>
       </c>
       <c r="Q7" t="n">
-        <v>2892</v>
+        <v>3007</v>
       </c>
       <c r="R7" t="n">
         <v>47.2</v>
@@ -1579,34 +1579,34 @@
         <v>36</v>
       </c>
       <c r="T7" t="n">
-        <v>52.2</v>
+        <v>50</v>
       </c>
       <c r="U7" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="V7" t="n">
-        <v>61.3</v>
+        <v>59.4</v>
       </c>
       <c r="W7" t="n">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="X7" t="n">
-        <v>32.1</v>
+        <v>32.3</v>
       </c>
       <c r="Y7" t="n">
-        <v>828</v>
+        <v>831</v>
       </c>
       <c r="Z7" t="n">
-        <v>51.8</v>
+        <v>51.6</v>
       </c>
       <c r="AA7" t="n">
-        <v>56</v>
+        <v>64</v>
       </c>
       <c r="AB7" t="n">
-        <v>64.7</v>
+        <v>63.5</v>
       </c>
       <c r="AC7" t="n">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="AD7" t="n">
         <v>54.2</v>
@@ -1615,10 +1615,10 @@
         <v>24</v>
       </c>
       <c r="AF7" t="n">
-        <v>45.8</v>
+        <v>45.3</v>
       </c>
       <c r="AG7" t="n">
-        <v>177</v>
+        <v>179</v>
       </c>
     </row>
   </sheetData>

--- a/ui_runner/templates/graded_analysis_tabs_2026-05-20.xlsx
+++ b/ui_runner/templates/graded_analysis_tabs_2026-05-20.xlsx
@@ -909,13 +909,13 @@
         <v>3007</v>
       </c>
       <c r="E17" t="n">
-        <v>575</v>
+        <v>577</v>
       </c>
       <c r="F17" t="n">
-        <v>2432</v>
+        <v>2430</v>
       </c>
       <c r="G17" t="n">
-        <v>19.1</v>
+        <v>19.2</v>
       </c>
     </row>
   </sheetData>
@@ -1567,7 +1567,7 @@
         <v>96</v>
       </c>
       <c r="P7" t="n">
-        <v>19.1</v>
+        <v>19.2</v>
       </c>
       <c r="Q7" t="n">
         <v>3007</v>
